--- a/Model Validations/Month plan.xlsx
+++ b/Model Validations/Month plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important File\Crew Management\POC\Model Evaluation\Fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFADFEEE-38A3-46F4-BCE6-711DD63687D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCA0EC7-7D32-462F-B325-22B6E84D4EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
